--- a/src/litman_analysis/resources/templates/economic-simulator/standard-v1/template.xlsx
+++ b/src/litman_analysis/resources/templates/economic-simulator/standard-v1/template.xlsx
@@ -516,7 +516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,6 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -645,8 +644,8 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Criterio configurable
-(0–? p)</t>
+          <t>Puntuación técnica
+(0–0 p)</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -661,25 +660,20 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>Puntos no económicos</t>
+          <t>C cualitativo</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>C cualitativo</t>
+          <t>Umbral baja anormal</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>Umbral baja anormal</t>
+          <t>Estado</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-      <c r="K14" s="6" t="inlineStr">
         <is>
           <t>Posición</t>
         </is>
@@ -706,22 +700,18 @@
         <v/>
       </c>
       <c r="G15" s="7">
-        <f>IF(B15="","",SUM(D15:D15))</f>
+        <f>IF(OR(B15="",D15=""),"",IFERROR(D15/$G$7,0))</f>
         <v/>
       </c>
       <c r="H15" s="7">
-        <f>IF(B15="","",IFERROR(G15/$G$7,0))</f>
+        <f>""</f>
         <v/>
       </c>
       <c r="I15" s="7">
-        <f>""</f>
+        <f>IF(B15="","",IF(H15="","NO CALCULABLE",IF(B15&lt;=H15,"POSIBLE BAJA ANORMAL","NORMAL")))</f>
         <v/>
       </c>
       <c r="J15" s="7">
-        <f>IF(B15="","",IF(I15="","NO CALCULABLE",IF(B15&lt;=I15,"POSIBLE BAJA ANORMAL","NORMAL")))</f>
-        <v/>
-      </c>
-      <c r="K15" s="7">
         <f>IF(F15="","",RANK(F15,$F$15:$F$16,0))</f>
         <v/>
       </c>
@@ -747,36 +737,32 @@
         <v/>
       </c>
       <c r="G16" s="7">
-        <f>IF(B16="","",SUM(D16:D16))</f>
+        <f>IF(OR(B16="",D16=""),"",IFERROR(D16/$G$7,0))</f>
         <v/>
       </c>
       <c r="H16" s="7">
-        <f>IF(B16="","",IFERROR(G16/$G$7,0))</f>
+        <f>""</f>
         <v/>
       </c>
       <c r="I16" s="7">
-        <f>""</f>
+        <f>IF(B16="","",IF(H16="","NO CALCULABLE",IF(B16&lt;=H16,"POSIBLE BAJA ANORMAL","NORMAL")))</f>
         <v/>
       </c>
       <c r="J16" s="7">
-        <f>IF(B16="","",IF(I16="","NO CALCULABLE",IF(B16&lt;=I16,"POSIBLE BAJA ANORMAL","NORMAL")))</f>
-        <v/>
-      </c>
-      <c r="K16" s="7">
         <f>IF(F16="","",RANK(F16,$F$15:$F$16,0))</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A1:K2"/>
-    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="A3:J3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J15:J16">
+  <conditionalFormatting sqref="I15:I16">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>J15="POSIBLE BAJA ANORMAL"</formula>
+      <formula>I15="POSIBLE BAJA ANORMAL"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
@@ -784,17 +770,15 @@
       <formula1>0.01</formula1>
       <formula2>1E+15</formula2>
     </dataValidation>
-    <dataValidation sqref="D15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Puntuación no válida" error="La puntuación debe estar dentro del rango del criterio." type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
+    <dataValidation sqref="D15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Puntuación técnica no válida" error="La puntuación técnica debe estar dentro del rango permitido." type="list">
+      <formula1>"0"</formula1>
     </dataValidation>
     <dataValidation sqref="B16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Precio no válido" error="El precio debe ser positivo y no superar el presupuesto máximo." type="decimal" operator="between">
       <formula1>0.01</formula1>
       <formula2>1E+15</formula2>
     </dataValidation>
-    <dataValidation sqref="D16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Puntuación no válida" error="La puntuación debe estar dentro del rango del criterio." type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>0</formula2>
+    <dataValidation sqref="D16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Puntuación técnica no válida" error="La puntuación técnica debe estar dentro del rango permitido." type="list">
+      <formula1>"0"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -903,7 +887,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Plantilla neutra: generar desde un dossier validado de Análisis 2.</t>
+          <t>Plantilla neutra: generar desde un dossier validado.</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1099,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Plantilla neutra: generar desde un dossier validado de Análisis 2.</t>
+          <t>Plantilla neutra: generar desde un dossier validado.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Análisis 2</t>
+          <t>Validación</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
